--- a/results/monthly_investor_report_2026-07-16.xlsx
+++ b/results/monthly_investor_report_2026-07-16.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -977,7 +977,7 @@
         <v>0.1047501547505572</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1361.849145534137</v>
+        <v>1361.849145534138</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>336.9487971989199</v>
@@ -1020,7 +1020,7 @@
         <v>0.0436044762683809</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>480.7314187874006</v>
+        <v>480.7314187874007</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>344.3894771685657</v>
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09676731342591428</v>
+        <v>0.09676731342591423</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9676.731342591429</v>
+        <v>9676.731342591424</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.07687214851712661</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>743.8711289280222</v>
+        <v>743.8711289280219</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>379.5974323522872</v>
@@ -1070,7 +1070,7 @@
         <v>329.6993168810639</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.188448267577676</v>
+        <v>1.188448267577674</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09533883249165311</v>
+        <v>0.09533883249165313</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9533.88324916531</v>
+        <v>9533.883249165314</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.025967427052516</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>247.5704177999044</v>
+        <v>247.5704177999045</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>202.1155831293457</v>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.06763640027756311</v>
+        <v>0.06763640027756314</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6763.640027756311</v>
+        <v>6763.640027756313</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0333833966972141</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>225.7932781637451</v>
+        <v>225.7932781637452</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>46.50225285137464</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>42.69473037002698</v>
+        <v>42.69473037002699</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.6516603662506142</v>
+        <v>0.6516603662506162</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>197</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>-0.0031018113855404</v>
+        <v>-0.0031018113855402</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>0.025967427052516</v>
@@ -1685,7 +1685,7 @@
         <v>0.0466708728798923</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>196.3889431570485</v>
+        <v>196.3889431570486</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>202.1155831293457</v>
@@ -1739,7 +1739,7 @@
         <v>-0.0157858315348814</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.0139753607082788</v>
+        <v>0.013975360708279</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>105.2899748041481</v>
@@ -1967,7 +1967,7 @@
         <v>0.0333833966972141</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>0.1048109348623858</v>
+        <v>0.1048109348623857</v>
       </c>
       <c r="H17" s="19" t="n">
         <v>43.47836758137415</v>
@@ -1979,7 +1979,7 @@
         <v>49.71649206880736</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>42.69473037002698</v>
+        <v>42.69473037002699</v>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>90.30000305175781</v>
+        <v>90.3000030517578</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>-0.1036950453198939</v>
@@ -2027,16 +2027,16 @@
         <v>0.0283370511511488</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>80.93634014291922</v>
+        <v>80.93634014291921</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>87.90467175975154</v>
+        <v>87.90467175975152</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>92.85883885718435</v>
+        <v>92.85883885718434</v>
       </c>
       <c r="K18" s="22" t="n">
-        <v>80.93634014291922</v>
+        <v>80.93634014291921</v>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>-0.0361423551605843</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>0.1552276165943749</v>
@@ -2087,7 +2087,7 @@
         <v>161.6389240981099</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>167.5813122101955</v>
+        <v>167.5813122101956</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>193.7316677774018</v>
@@ -2162,7 +2162,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.2699645419310046</v>
+        <v>0.2699645419310044</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.0700934579439251</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.3637918713419257</v>
+        <v>0.3637918713419255</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0.021181247850716</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="J5" s="17" t="n">
-        <v>0.0238092956020326</v>
+        <v>0.0238092956020327</v>
       </c>
       <c r="K5" s="17" t="n">
         <v>-0.0267075881338385</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.0248090483605681</v>
+        <v>0.024809048360568</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>0.1047501547505572</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>-0.0154922839028397</v>
+        <v>-0.0154922839028396</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>-0.0450799947367163</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.0210928877011063</v>
+        <v>0.0210928877011062</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>0.025967427052516</v>
@@ -2471,7 +2471,7 @@
         <v>-0.0260416673565352</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>-0.035253705897935</v>
+        <v>-0.0352537058979348</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0.1032448408562265</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.0218090949713451</v>
+        <v>0.0218090949713452</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>-0.0157858315348814</v>
@@ -2517,7 +2517,7 @@
         <v>0.4195514021586155</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.7472256708514629</v>
+        <v>0.7472256708514631</v>
       </c>
       <c r="H10" s="17" t="n">
         <v>-0.0966077990495649</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="J11" s="20" t="n">
-        <v>0.0323413944949448</v>
+        <v>0.0323413944949449</v>
       </c>
       <c r="K11" s="20" t="n">
         <v>0.07687214851712661</v>
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="E13" s="20" t="n">
-        <v>-0.0204614422030583</v>
+        <v>-0.0204614422030581</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>-0.0518956693664893</v>
+        <v>-0.0518956693664892</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>0.1846376939669889</v>
+        <v>0.1846376939669887</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>-0.08927798507305711</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J13" s="20" t="n">
-        <v>0.0256141069997002</v>
+        <v>0.0256141069997001</v>
       </c>
       <c r="K13" s="20" t="n">
         <v>0.0333833966972141</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0294643191802923</v>
+        <v>0.0294643191802922</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0558806111879733</v>
+        <v>0.0558806111879734</v>
       </c>
     </row>
     <row r="15">
@@ -2729,10 +2729,10 @@
         <v>-0.1041666635129818</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.1014925069476834</v>
+        <v>-0.1014925069476836</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>-0.0176581311770364</v>
+        <v>-0.0176581311770365</v>
       </c>
       <c r="H15" s="23" t="n">
         <v>-0.0323755999692956</v>
@@ -2815,10 +2815,10 @@
         <v>-0.0885869731073794</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.1036879130006019</v>
+        <v>-0.1036879130006018</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-0.1491629033224522</v>
+        <v>-0.149162903322452</v>
       </c>
       <c r="H17" s="23" t="n">
         <v>-0.0486293813820859</v>
@@ -2832,7 +2832,7 @@
         <v>0.0209242476671809</v>
       </c>
       <c r="K17" s="23" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
     </row>
     <row r="18">
@@ -2858,7 +2858,7 @@
         <v>-0.0630331898187573</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.1608659090552879</v>
+        <v>-0.1608659090552878</v>
       </c>
       <c r="G18" s="25" t="n">
         <v>-0.1134529284832188</v>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0165367731826493</v>
+        <v>0.0165367731826494</v>
       </c>
       <c r="K18" s="25" t="n">
         <v>0.0531914626506075</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0293944691265913</v>
+        <v>0.0293944691265912</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>0.0999999916062814</v>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.0755750415689177</v>
+        <v>-0.07557504156891739</v>
       </c>
       <c r="F20" s="25" t="n">
         <v>-0.2045240081085867</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1407812215898962</v>
+        <v>-0.1407812215898961</v>
       </c>
       <c r="H20" s="25" t="n">
         <v>-0.1771614345863863</v>
@@ -2994,7 +2994,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3113,7 +3113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3489,7 +3489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
         <v>454.9145851775429</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3596,7 +3596,7 @@
         <v>-329.6703296703308</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3626,7 +3626,7 @@
         <v>-134.212405797778</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3656,7 +3656,7 @@
         <v>-82879.96970578819</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3686,7 +3686,7 @@
         <v>-2751.438172919472</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3716,7 +3716,7 @@
         <v>-8189.448336457834</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.039937230347891</v>

--- a/results/monthly_investor_report_2026-07-16.xlsx
+++ b/results/monthly_investor_report_2026-07-16.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2162,7 +2162,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3113,7 +3113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3489,7 +3489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
         <v>454.9145851775429</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3596,7 +3596,7 @@
         <v>-329.6703296703308</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3626,7 +3626,7 @@
         <v>-134.212405797778</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3656,7 +3656,7 @@
         <v>-82879.96970578819</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3686,7 +3686,7 @@
         <v>-2751.438172919472</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3716,7 +3716,7 @@
         <v>-8189.448336457834</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.039937230347891</v>
